--- a/artfynd/A 23815-2023 artfynd.xlsx
+++ b/artfynd/A 23815-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23815-2023 artfynd.xlsx
+++ b/artfynd/A 23815-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,254 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120336850</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vackelberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552422</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6703555</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>9 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120336845</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vackelberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552459</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6703494</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23815-2023 artfynd.xlsx
+++ b/artfynd/A 23815-2023 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120336850</v>
+        <v>120336845</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552422</v>
+        <v>552459</v>
       </c>
       <c r="R4" t="n">
-        <v>6703555</v>
+        <v>6703494</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>9 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120336845</v>
+        <v>120336850</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552459</v>
+        <v>552422</v>
       </c>
       <c r="R5" t="n">
-        <v>6703494</v>
+        <v>6703555</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>9 blomstjälkar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 23815-2023 artfynd.xlsx
+++ b/artfynd/A 23815-2023 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120336845</v>
+        <v>120336850</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552459</v>
+        <v>552422</v>
       </c>
       <c r="R4" t="n">
-        <v>6703494</v>
+        <v>6703555</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 blomstjälk</t>
+          <t>9 blomstjälkar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120336850</v>
+        <v>120336845</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552422</v>
+        <v>552459</v>
       </c>
       <c r="R5" t="n">
-        <v>6703555</v>
+        <v>6703494</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>9 blomstjälkar</t>
+          <t>1 blomstjälk</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 23815-2023 artfynd.xlsx
+++ b/artfynd/A 23815-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111408013</v>
+        <v>111407996</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,18 +703,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vackelberget (Vackelberget), Dlr</t>
+          <t>Vackelberget, Vackelberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552471.8765200907</v>
+        <v>552411</v>
       </c>
       <c r="R2" t="n">
-        <v>6703516.674196084</v>
+        <v>6703547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,19 +748,9 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111407996</v>
+        <v>111408013</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,22 +805,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vackelberget (Vackelberget), Dlr</t>
+          <t>Vackelberget, Vackelberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552410.6667086715</v>
+        <v>552472</v>
       </c>
       <c r="R3" t="n">
-        <v>6703546.864278791</v>
+        <v>6703517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +858,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,12 +888,7 @@
         <v>120336845</v>
       </c>
       <c r="B4" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1032,12 +1007,7 @@
         <v>120336850</v>
       </c>
       <c r="B5" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
